--- a/fake data/03_Student_Enrollment.xlsx
+++ b/fake data/03_Student_Enrollment.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rd40cff1905dc416c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enrollment by Major" sheetId="2" r:id="Rf663737eb69e482a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cohort Groups" sheetId="3" r:id="R3ad37a5ce9364a72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" r:id="R8b1b2468ecee4157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R1d36a24812bb4fe4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enrollment by Major" sheetId="2" r:id="Ra230b0aee061424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cohort Groups" sheetId="3" r:id="R6334411ded60455b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" r:id="R58503ca072a54e1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -107,7 +107,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -141,6 +141,9 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -372,7 +375,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R75268e75481b441d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2bcfdf44043d48a2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -833,7 +836,7 @@
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
       <x:c r="A23" s="19" t="str">
-        <x:v>Each year cohort is split into tutorial groups of no more than 25 students.</x:v>
+        <x:v>Each tutorial group contains no more than 25 students, belongs to exactly one major, and may never share a tutorial or lab with another major.</x:v>
       </x:c>
       <x:c r="B23" s="19"/>
       <x:c r="C23" s="19"/>
@@ -854,7 +857,7 @@
     <x:mergeCell ref="A23:K23"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1ae95ce216645a4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R290aa2f6fe824841"/>
 </x:worksheet>
 </file>
 
@@ -1819,7 +1822,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb89f1c88dc2840cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbebcad6de1bc4588"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19369,7 +19372,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R044aa781a4f94379"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra55c0b15a4924c28"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19450,12 +19453,12 @@
         <x:v>15 minutes after Periods 1, 2, and 3; 30 minutes after Period 4.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="20" customHeight="1">
-      <x:c r="A11" s="20" t="str">
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="22" t="str">
         <x:v>Shared courses</x:v>
       </x:c>
-      <x:c r="B11" s="20" t="str">
-        <x:v>Shared-course lectures may combine majors; tutorials/labs always remain major-specific.</x:v>
+      <x:c r="B11" s="22" t="str">
+        <x:v>Only lectures may combine majors. Tutorials and labs must be scheduled separately for one major and one cohort group.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20" customHeight="1">
@@ -19473,7 +19476,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d7188093b2646b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ca26391a90a47be"/>
   </x:tableParts>
 </x:worksheet>
 </file>